--- a/LISTAS/mi/PITONES.xlsx
+++ b/LISTAS/mi/PITONES.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45183.57417124406</v>
+        <v>45253</v>
       </c>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
@@ -939,25 +939,6 @@
       <c r="F10" s="15" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="27" customHeight="1" s="30">
       <c r="A30" s="29" t="inlineStr">
         <is>
@@ -1019,7 +1000,7 @@
         <v>50</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>1186.114</v>
+        <v>1304.725</v>
       </c>
       <c r="N34" s="20" t="n"/>
     </row>
@@ -1038,7 +1019,7 @@
         <v>50</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>1581.484</v>
+        <v>1739.632</v>
       </c>
       <c r="N35" s="20" t="n"/>
     </row>
@@ -1057,7 +1038,7 @@
         <v>50</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>2290.824</v>
+        <v>2519.906</v>
       </c>
       <c r="N36" s="20" t="n"/>
     </row>
@@ -1076,11 +1057,10 @@
         <v>25</v>
       </c>
       <c r="D37" s="17" t="n">
-        <v>1948.243</v>
+        <v>2143.067</v>
       </c>
       <c r="N37" s="20" t="n"/>
     </row>
-    <row r="38"/>
     <row r="39" ht="26.25" customHeight="1" s="30">
       <c r="A39" s="28" t="inlineStr">
         <is>
@@ -1128,7 +1108,7 @@
         <v>100</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>1523.339</v>
+        <v>1675.673</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="30">
@@ -1146,7 +1126,7 @@
         <v>100</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>2012.632</v>
+        <v>2213.895</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="30">
@@ -1164,7 +1144,7 @@
         <v>100</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>2535.019</v>
+        <v>2788.521</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1" s="30" thickBot="1">
@@ -1182,16 +1162,9 @@
         <v>50</v>
       </c>
       <c r="D44" s="19" t="n">
-        <v>2215.678</v>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
+        <v>2437.246</v>
+      </c>
+    </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -1201,10 +1174,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/PITONES.xlsx
+++ b/LISTAS/mi/PITONES.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>

--- a/LISTAS/mi/PITONES.xlsx
+++ b/LISTAS/mi/PITONES.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>

--- a/LISTAS/mi/PITONES.xlsx
+++ b/LISTAS/mi/PITONES.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>

--- a/LISTAS/mi/PITONES.xlsx
+++ b/LISTAS/mi/PITONES.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45266</v>
+        <v>45264.54809718801</v>
       </c>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
@@ -939,6 +939,25 @@
       <c r="F10" s="15" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30" ht="27" customHeight="1" s="30">
       <c r="A30" s="29" t="inlineStr">
         <is>
@@ -1000,7 +1019,7 @@
         <v>50</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>1304.725</v>
+        <v>1736.01</v>
       </c>
       <c r="N34" s="20" t="n"/>
     </row>
@@ -1019,7 +1038,7 @@
         <v>50</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>1739.632</v>
+        <v>2314.68</v>
       </c>
       <c r="N35" s="20" t="n"/>
     </row>
@@ -1038,7 +1057,7 @@
         <v>50</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>2519.906</v>
+        <v>3352.88</v>
       </c>
       <c r="N36" s="20" t="n"/>
     </row>
@@ -1057,10 +1076,11 @@
         <v>25</v>
       </c>
       <c r="D37" s="17" t="n">
-        <v>2143.067</v>
+        <v>2851.48</v>
       </c>
       <c r="N37" s="20" t="n"/>
     </row>
+    <row r="38"/>
     <row r="39" ht="26.25" customHeight="1" s="30">
       <c r="A39" s="28" t="inlineStr">
         <is>
@@ -1108,7 +1128,7 @@
         <v>100</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>1675.673</v>
+        <v>2229.58</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="30">
@@ -1126,7 +1146,7 @@
         <v>100</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>2213.895</v>
+        <v>2945.72</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="30">
@@ -1144,7 +1164,7 @@
         <v>100</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>2788.521</v>
+        <v>3710.29</v>
       </c>
     </row>
     <row r="44" ht="18.75" customHeight="1" s="30" thickBot="1">
@@ -1162,9 +1182,16 @@
         <v>50</v>
       </c>
       <c r="D44" s="19" t="n">
-        <v>2437.246</v>
-      </c>
-    </row>
+        <v>3242.9</v>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -1174,10 +1201,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
